--- a/KatalonData/ABPTestDataDemo/ABPEditUser.xlsx
+++ b/KatalonData/ABPTestDataDemo/ABPEditUser.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CEB47F3-CC1E-4FC9-9AD1-B2048210C118}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5BA354-8422-47B3-BA29-C28E8A7CDE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{1DD8A320-6572-432F-97F4-1D86BCB29215}"/>
   </bookViews>
@@ -24,7 +24,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="30">
   <si>
     <t>Result</t>
   </si>
@@ -108,55 +108,7 @@
     <t>create Owner+ change- First Name, Last Name, Email, Phone+ verify User Name, Name, Role, edit, delete links (non logged in user)</t>
   </si>
   <si>
-    <t>Sun Aug 23 22:55:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 24 20:38:51 IST 2026</t>
-  </si>
-  <si>
-    <t>2026-08-24 21:04:31</t>
-  </si>
-  <si>
-    <t>2026-08-24 21:17:50</t>
-  </si>
-  <si>
-    <t>Mon Aug 24 21:28:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Aug 24 21:33:09 IST 2026</t>
-  </si>
-  <si>
     <t>create Payer+ delete Payer</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:20:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:24:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:39:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:40:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:41:05 IST 2026</t>
-  </si>
-  <si>
-    <t>2026-08-25 18:41:34</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:43:37 IST 2026</t>
-  </si>
-  <si>
-    <t>2026-08-25 18:44:17</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:44:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Tue Aug 25 18:45:21 IST 2026</t>
   </si>
   <si>
     <t>Tue Aug 25 18:52:54 IST 2026</t>
@@ -187,7 +139,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -603,14 +554,14 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="8.7265625"/>
-    <col min="2" max="2" customWidth="true" style="3" width="14.90625"/>
-    <col min="3" max="3" customWidth="true" style="4" width="62.7265625"/>
-    <col min="4" max="4" style="3" width="8.7265625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="19.81640625"/>
-    <col min="6" max="6" customWidth="true" style="3" width="19.81640625"/>
-    <col min="7" max="7" customWidth="true" style="3" width="22.54296875"/>
-    <col min="8" max="16384" style="3" width="8.7265625"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="14.90625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="62.7265625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.54296875" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -641,10 +592,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -690,14 +641,14 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="8.7265625"/>
-    <col min="2" max="2" customWidth="true" style="3" width="14.90625"/>
-    <col min="3" max="3" customWidth="true" style="4" width="62.7265625"/>
-    <col min="4" max="4" style="3" width="8.7265625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="19.81640625"/>
-    <col min="6" max="6" customWidth="true" style="3" width="19.81640625"/>
-    <col min="7" max="7" customWidth="true" style="3" width="22.54296875"/>
-    <col min="8" max="16384" style="3" width="8.7265625"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="14.90625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="62.7265625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.54296875" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -728,10 +679,10 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -777,14 +728,14 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="8.7265625"/>
-    <col min="2" max="2" customWidth="true" style="3" width="13.26953125"/>
-    <col min="3" max="3" customWidth="true" style="3" width="54.36328125"/>
-    <col min="4" max="4" style="3" width="8.7265625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="19.81640625"/>
-    <col min="6" max="6" customWidth="true" style="3" width="17.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="3" width="18.81640625"/>
-    <col min="8" max="16384" style="3" width="8.7265625"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="13.26953125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="54.36328125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
@@ -815,7 +766,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>17</v>
@@ -847,14 +798,14 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="8.7265625"/>
-    <col min="2" max="2" customWidth="true" style="3" width="14.90625"/>
-    <col min="3" max="3" customWidth="true" style="4" width="62.7265625"/>
-    <col min="4" max="4" style="3" width="8.7265625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="19.81640625"/>
-    <col min="6" max="6" customWidth="true" style="3" width="19.81640625"/>
-    <col min="7" max="7" customWidth="true" style="3" width="22.54296875"/>
-    <col min="8" max="16384" style="3" width="8.7265625"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="14.90625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="62.7265625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.54296875" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -885,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>19</v>
@@ -934,14 +885,14 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="8.7265625"/>
-    <col min="2" max="2" customWidth="true" style="3" width="13.26953125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="3" width="52.7265625"/>
-    <col min="4" max="4" style="3" width="8.7265625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="19.81640625"/>
-    <col min="6" max="6" customWidth="true" style="3" width="17.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="3" width="18.81640625"/>
-    <col min="8" max="16384" style="3" width="8.7265625"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="13.26953125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="52.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
@@ -972,7 +923,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
@@ -1004,14 +955,14 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="8.7265625"/>
-    <col min="2" max="2" customWidth="true" style="3" width="13.26953125"/>
-    <col min="3" max="3" customWidth="true" style="3" width="54.36328125"/>
-    <col min="4" max="4" style="3" width="8.7265625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="19.81640625"/>
-    <col min="6" max="6" customWidth="true" style="3" width="17.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="3" width="18.81640625"/>
-    <col min="8" max="16384" style="3" width="8.7265625"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="13.26953125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="54.36328125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
@@ -1042,7 +993,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>16</v>
@@ -1074,14 +1025,14 @@
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="8.7265625"/>
-    <col min="2" max="2" customWidth="true" style="3" width="14.453125"/>
-    <col min="3" max="3" customWidth="true" style="4" width="64.1796875"/>
-    <col min="4" max="4" style="3" width="8.7265625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="19.81640625"/>
-    <col min="6" max="6" customWidth="true" style="3" width="19.81640625"/>
-    <col min="7" max="7" customWidth="true" style="3" width="22.54296875"/>
-    <col min="8" max="16384" style="3" width="8.7265625"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="14.453125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="64.1796875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="22.54296875" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1112,7 +1063,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>20</v>
@@ -1161,14 +1112,14 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="8.7265625"/>
-    <col min="2" max="2" customWidth="true" style="3" width="13.26953125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="3" width="52.7265625"/>
-    <col min="4" max="4" style="3" width="8.7265625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="19.81640625"/>
-    <col min="6" max="6" customWidth="true" style="3" width="17.81640625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="3" width="18.81640625"/>
-    <col min="8" max="16384" style="3" width="8.7265625"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
+    <col min="2" max="2" width="13.26953125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="52.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="3"/>
+    <col min="5" max="5" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="18.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
@@ -1199,7 +1150,7 @@
         <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
